--- a/data/P2/Multiplier table.xlsx
+++ b/data/P2/Multiplier table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/Math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC46117F-F6D3-B74F-90E9-4C8CD50BDBAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F15A02-6B9D-AF4C-8A46-00B0AF7E0B8A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="3600" windowWidth="26660" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>word</t>
   </si>
@@ -608,6 +608,78 @@
   </si>
   <si>
     <t>沒有句子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>one ten 10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>two ten 20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>three ten 30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>four ten 40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>five ten 50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>six ten 60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>seven ten 70</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eight ten 80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 × 10 =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nine ten 90</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9 × 10 =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1015,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -1144,21 +1216,22 @@
     </row>
     <row r="11" spans="1:7" ht="30" thickBot="1">
       <c r="A11" s="7" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>11</v>
+        <v>170</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="30" thickBot="1">
       <c r="A12" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -1166,10 +1239,10 @@
     </row>
     <row r="13" spans="1:7" ht="30" thickBot="1">
       <c r="A13" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -1177,10 +1250,10 @@
     </row>
     <row r="14" spans="1:7" ht="30" thickBot="1">
       <c r="A14" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
@@ -1188,10 +1261,10 @@
     </row>
     <row r="15" spans="1:7" ht="30" thickBot="1">
       <c r="A15" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
@@ -1199,10 +1272,10 @@
     </row>
     <row r="16" spans="1:7" ht="30" thickBot="1">
       <c r="A16" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
@@ -1210,10 +1283,10 @@
     </row>
     <row r="17" spans="1:3" ht="30" thickBot="1">
       <c r="A17" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
@@ -1221,10 +1294,10 @@
     </row>
     <row r="18" spans="1:3" ht="30" thickBot="1">
       <c r="A18" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
@@ -1232,10 +1305,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" thickBot="1">
       <c r="A19" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
@@ -1243,32 +1316,32 @@
     </row>
     <row r="20" spans="1:3" ht="30" thickBot="1">
       <c r="A20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" thickBot="1">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" thickBot="1">
       <c r="A22" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -1276,10 +1349,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" thickBot="1">
       <c r="A23" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -1287,10 +1360,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" thickBot="1">
       <c r="A24" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
@@ -1298,10 +1371,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" thickBot="1">
       <c r="A25" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
@@ -1309,10 +1382,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" thickBot="1">
       <c r="A26" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
@@ -1320,10 +1393,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" thickBot="1">
       <c r="A27" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2">
         <v>3</v>
@@ -1331,10 +1404,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" thickBot="1">
       <c r="A28" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -1342,43 +1415,43 @@
     </row>
     <row r="29" spans="1:3" ht="30" thickBot="1">
       <c r="A29" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="30" thickBot="1">
       <c r="A30" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30" thickBot="1">
       <c r="A31" s="7" t="s">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="C31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" thickBot="1">
       <c r="A32" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2">
         <v>4</v>
@@ -1386,10 +1459,10 @@
     </row>
     <row r="33" spans="1:3" ht="30" thickBot="1">
       <c r="A33" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C33" s="2">
         <v>4</v>
@@ -1397,10 +1470,10 @@
     </row>
     <row r="34" spans="1:3" ht="30" thickBot="1">
       <c r="A34" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C34" s="2">
         <v>4</v>
@@ -1408,10 +1481,10 @@
     </row>
     <row r="35" spans="1:3" ht="30" thickBot="1">
       <c r="A35" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C35" s="2">
         <v>4</v>
@@ -1419,10 +1492,10 @@
     </row>
     <row r="36" spans="1:3" ht="30" thickBot="1">
       <c r="A36" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C36" s="2">
         <v>4</v>
@@ -1430,10 +1503,10 @@
     </row>
     <row r="37" spans="1:3" ht="30" thickBot="1">
       <c r="A37" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C37" s="2">
         <v>4</v>
@@ -1441,54 +1514,54 @@
     </row>
     <row r="38" spans="1:3" ht="30" thickBot="1">
       <c r="A38" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="8">
-        <v>5</v>
+        <v>38</v>
+      </c>
+      <c r="C38" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="30" thickBot="1">
       <c r="A39" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" s="8">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="C39" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="30" thickBot="1">
       <c r="A40" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="8">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="C40" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="30" thickBot="1">
       <c r="A41" s="7" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="8">
-        <v>5</v>
+        <v>176</v>
+      </c>
+      <c r="C41" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="30" thickBot="1">
       <c r="A42" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C42" s="8">
         <v>5</v>
@@ -1496,10 +1569,10 @@
     </row>
     <row r="43" spans="1:3" ht="30" thickBot="1">
       <c r="A43" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C43" s="8">
         <v>5</v>
@@ -1507,10 +1580,10 @@
     </row>
     <row r="44" spans="1:3" ht="30" thickBot="1">
       <c r="A44" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C44" s="8">
         <v>5</v>
@@ -1518,10 +1591,10 @@
     </row>
     <row r="45" spans="1:3" ht="30" thickBot="1">
       <c r="A45" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C45" s="8">
         <v>5</v>
@@ -1529,10 +1602,10 @@
     </row>
     <row r="46" spans="1:3" ht="30" thickBot="1">
       <c r="A46" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C46" s="8">
         <v>5</v>
@@ -1540,65 +1613,65 @@
     </row>
     <row r="47" spans="1:3" ht="30" thickBot="1">
       <c r="A47" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C47" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" thickBot="1">
       <c r="A48" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C48" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" thickBot="1">
       <c r="A49" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C49" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" thickBot="1">
       <c r="A50" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C50" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="30" thickBot="1">
       <c r="A51" s="7" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="8">
-        <v>6</v>
+        <v>178</v>
+      </c>
+      <c r="C51" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="30" thickBot="1">
       <c r="A52" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C52" s="8">
         <v>6</v>
@@ -1606,10 +1679,10 @@
     </row>
     <row r="53" spans="1:3" ht="30" thickBot="1">
       <c r="A53" s="7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C53" s="8">
         <v>6</v>
@@ -1617,10 +1690,10 @@
     </row>
     <row r="54" spans="1:3" ht="30" thickBot="1">
       <c r="A54" s="7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C54" s="8">
         <v>6</v>
@@ -1628,10 +1701,10 @@
     </row>
     <row r="55" spans="1:3" ht="30" thickBot="1">
       <c r="A55" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C55" s="8">
         <v>6</v>
@@ -1639,76 +1712,76 @@
     </row>
     <row r="56" spans="1:3" ht="30" thickBot="1">
       <c r="A56" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="C56" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="30" thickBot="1">
       <c r="A57" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="C57" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="30" thickBot="1">
       <c r="A58" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="C58" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="30" thickBot="1">
       <c r="A59" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="C59" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="30" thickBot="1">
       <c r="A60" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="C60" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="30" thickBot="1">
       <c r="A61" s="7" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C61" s="8">
-        <v>7</v>
+        <v>180</v>
+      </c>
+      <c r="C61" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="30" thickBot="1">
       <c r="A62" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C62" s="8">
         <v>7</v>
@@ -1716,10 +1789,10 @@
     </row>
     <row r="63" spans="1:3" ht="30" thickBot="1">
       <c r="A63" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C63" s="8">
         <v>7</v>
@@ -1727,10 +1800,10 @@
     </row>
     <row r="64" spans="1:3" ht="30" thickBot="1">
       <c r="A64" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C64" s="8">
         <v>7</v>
@@ -1738,87 +1811,87 @@
     </row>
     <row r="65" spans="1:3" ht="30" thickBot="1">
       <c r="A65" s="7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C65" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="30" thickBot="1">
       <c r="A66" s="7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C66" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="30" thickBot="1">
       <c r="A67" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C67" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="30" thickBot="1">
       <c r="A68" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C68" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="30" thickBot="1">
       <c r="A69" s="7" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C69" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="30" thickBot="1">
       <c r="A70" s="7" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C70" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="30" thickBot="1">
       <c r="A71" s="7" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C71" s="8">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="C71" s="2">
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="30" thickBot="1">
       <c r="A72" s="7" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C72" s="8">
         <v>8</v>
@@ -1826,10 +1899,10 @@
     </row>
     <row r="73" spans="1:3" ht="30" thickBot="1">
       <c r="A73" s="7" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C73" s="8">
         <v>8</v>
@@ -1837,100 +1910,199 @@
     </row>
     <row r="74" spans="1:3" ht="30" thickBot="1">
       <c r="A74" s="7" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C74" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="30" thickBot="1">
       <c r="A75" s="7" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C75" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="30" thickBot="1">
       <c r="A76" s="7" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C76" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="30" thickBot="1">
       <c r="A77" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C77" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="30" thickBot="1">
       <c r="A78" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C78" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="30" thickBot="1">
       <c r="A79" s="7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C79" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="30" thickBot="1">
       <c r="A80" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C80" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="30" thickBot="1">
       <c r="A81" s="7" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C81" s="8">
-        <v>9</v>
+        <v>184</v>
+      </c>
+      <c r="C81" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="30" thickBot="1">
       <c r="A82" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="30" thickBot="1">
+      <c r="A83" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C83" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="30" thickBot="1">
+      <c r="A84" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="30" thickBot="1">
+      <c r="A85" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="30" thickBot="1">
+      <c r="A86" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C86" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="30" thickBot="1">
+      <c r="A87" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C87" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="30" thickBot="1">
+      <c r="A88" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C88" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="30" thickBot="1">
+      <c r="A89" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C89" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="30" thickBot="1">
+      <c r="A90" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B90" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C82" s="8">
+      <c r="C90" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="30" thickBot="1">
+      <c r="A91" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C91" s="2">
         <v>9</v>
       </c>
     </row>
